--- a/site/exports/nwsuaf-forestry.xlsx
+++ b/site/exports/nwsuaf-forestry.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导师'!$A$1:$L$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,18 +443,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="19.6" customWidth="1" min="3" max="3"/>
-    <col width="64.39999999999999" customWidth="1" min="4" max="4"/>
+    <col width="65" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
-    <col width="26.6" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="40.59999999999999" customWidth="1" min="8" max="8"/>
+    <col width="23.8" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
@@ -477,7 +477,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>官方主页</t>
+          <t>个人主页／职业网站（来源类型见说明）</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>缺项与冲突</t>
+          <t>来源说明与待核事项</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -502,7 +502,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>替代官方职业报道（非个人主页）</t>
+          <t>替代职业资料来源（非已核个人主页）</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -569,10 +569,64 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>牛康任</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>校区未标注</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>林学院</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>https://cf.nwafu.edu.cn/szdw/zjrc2/46d132989cd143ec9470a59f9b94c10f.htm</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>未知（来源日期异常）</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>现职unknown；目录、历史角色与开放任期不等于观察日人事确认。；仅必要官网职业摘录与书目；未独立核出版元数据或全文。；来源级授位学校与独立法律实体、原始学位证核验不同；学习时间与授位时间分开。；目录原始href、页面文本链接导航和浏览器页面导航分别记载，不互相替代。；学士、博士两项来源明确获授及来源级授位学校保留；毕业年月不倒填独立授位年月。；合作者Kuiyan Song不转为本人导师；硕士未披露不补。；个人页与目录单位、讲师与中级标签分别保留，不补行政父子链或职级变动。；学士、博士2项明确获授；毕业年月不独立充作授位年月，硕士未披露，不补事件。；来源级授位学校已由同句明确，不因授位法人未另核而降为学校未知。；本人导师未披露；论文合作者Kuiyan Song不能反推本人导师，硕士生导师为招生资格。；个人页家具与室内设计教研室和目录木材科学与工程系分别保留，不强推未明示的行政父子关系。；目录中级与个人页讲师为不同粒度标签，不据此声称职级变更；现职仍unknown。；两条官网论文作者完整保留但角色null，未核外部元数据或全文。</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>分批核实资料，不是完整名录；NEW_RECOVERY：基于留存公开职业来源记录重建；必要事实仍有缺项，不代表完整履历或当前人事认证。；公开教学事实（非本人求学学历；教学／课程开设时间不是入学、授位或任职起点；不计入教育、任职、论文、导师统计及师承图）：家具史；承担课程；教学／课程开设时间：时间未披露；来源记载的教学内容，不代表当前开课；教学对象层次不属于本人学历。；教学对象层次：未知；来源ID：new-recovery-nwsuaf-niukangren-s001-1533706c096d；https://cf.nwafu.edu.cn/szdw/zjrc2/46d132989cd143ec9470a59f9b94c10f.htm | 创新创业论坛；承担课程；教学／课程开设时间：时间未披露；来源记载的教学内容，不代表当前开课；教学对象层次不属于本人学历。；教学对象层次：未知；来源ID：new-recovery-nwsuaf-niukangren-s001-1533706c096d；https://cf.nwafu.edu.cn/szdw/zjrc2/46d132989cd143ec9470a59f9b94c10f.htm；人物整体核验日期未单独记录</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>官方资料（原来源）；公开个人页（访问与内容时效见来源记录）</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>nwsuaf</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>西北农林科技大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K2"/>
+  <autoFilter ref="A1:K3"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -584,7 +638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S5"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -603,7 +657,7 @@
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="65" customWidth="1" min="15" max="15"/>
     <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="64.39999999999999" customWidth="1" min="17" max="17"/>
+    <col width="65" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
   </cols>
@@ -666,7 +720,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>确证授位</t>
+          <t>来源记载学位</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -935,13 +989,195 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>牛康任</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>工学学士</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>四川农业大学</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2013-06</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>同句毕业于该校并获学位，足以支持来源级授位学校；不需法律登记验证。时间原文指毕业月，不自动改为独立授位日期。专业、入学日期未披露。；explicit_award_wording_in_official_body；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源education_stage：本科；来源date_as_source：2013年6月</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t>https://cf.nwafu.edu.cn/szdw/zjrc2/46d132989cd143ec9470a59f9b94c10f.htm</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>nwsuaf</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>西北农林科技大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>牛康任</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>工学博士</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>东北林业大学</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2021-06</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>同句毕业于该校并获学位，足以支持来源级授位学校；不需法律登记验证。时间原文指毕业月，不自动改为独立授位日期。专业、入学日期未披露。；explicit_award_wording_in_official_body；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源education_stage：博士；来源date_as_source：2021年6月</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>https://cf.nwafu.edu.cn/szdw/zjrc2/46d132989cd143ec9470a59f9b94c10f.htm</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>nwsuaf</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>西北农林科技大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>牛康任</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>主任</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>西北农林科技大学</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>任职按留存来源表述保留；不据此认证当前人事状态。；来源记载（院系）：林学院；来源记载（单位）：家具与室内设计教研室</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>https://cf.nwafu.edu.cn/szdw/zjrc2/46d132989cd143ec9470a59f9b94c10f.htm</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>nwsuaf</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>西北农林科技大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S5"/>
+  <autoFilter ref="A1:S8"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1044,18 +1280,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="65" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="64.39999999999999" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="64.39999999999999" customWidth="1" min="7" max="7"/>
+    <col width="65" customWidth="1" min="5" max="5"/>
+    <col width="44.8" customWidth="1" min="6" max="6"/>
+    <col width="65" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="64.39999999999999" customWidth="1" min="9" max="9"/>
+    <col width="65" customWidth="1" min="9" max="9"/>
     <col width="65" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
@@ -1227,13 +1463,121 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>牛康任</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Surface coating and interfacial properties of hot-waxed wood using modified polyethylene wax</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>https://cf.nwafu.edu.cn/szdw/zjrc2/46d132989cd143ec9470a59f9b94c10f.htm</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>journal_article_as_official_list</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>https://cf.nwafu.edu.cn/szdw/zjrc2/46d132989cd143ec9470a59f9b94c10f.htm</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源authors_as_source：Kangren Niu, Kuiyan Song；来源书目信息（卷）：150；来源书目信息（文章编号）：105947</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>nwsuaf</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>西北农林科技大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>牛康任</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Hot waxing treatment improves the aging resistance of wood surface under UV radiation and water</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>https://cf.nwafu.edu.cn/szdw/zjrc2/46d132989cd143ec9470a59f9b94c10f.htm</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>journal_article_as_official_list</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>https://cf.nwafu.edu.cn/szdw/zjrc2/46d132989cd143ec9470a59f9b94c10f.htm</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源authors_as_source：Kangren Niu, Kuiyan Song；来源书目信息（卷）：161；来源书目信息（文章编号）：106468</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>nwsuaf</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>西北农林科技大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L3"/>
+  <autoFilter ref="A1:L5"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1245,14 +1589,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="64.39999999999999" customWidth="1" min="3" max="3"/>
+    <col width="65" customWidth="1" min="2" max="2"/>
+    <col width="65" customWidth="1" min="3" max="3"/>
     <col width="65" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="33.59999999999999" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
@@ -1368,11 +1712,87 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>牛康任</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-nwsuaf-niukangren-s001-1533706c096d</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>https://cf.nwafu.edu.cn/szdw/zjrc2/46d132989cd143ec9470a59f9b94c10f.htm</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T04:15:11.017Z</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>nwsuaf</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>西北农林科技大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>牛康任</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-nwsuaf-niukangren-s002-904c0e3267cb</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>https://cf.nwafu.edu.cn/szdw/zjrc2/index.htm</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T04:15:14.796Z</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>nwsuaf</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>西北农林科技大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
+  <autoFilter ref="A1:G5"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
